--- a/09_ai-transparency-documentation/demo/model_card_demo.xlsx
+++ b/09_ai-transparency-documentation/demo/model_card_demo.xlsx
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Disclosure obligations toward end users when they interact with AI systems — chatbot labels, deepfake labels, emotion recognition / biometric categorisation notice. Deployer obligation. Lives outside the Article 11 stack but cross-references it when end-user disclosure is needed.</t>
+          <t>Disclosure obligations toward end users when they interact with AI systems — provider duty for direct-interaction (chatbot) labels and synthetic-content marking (Art. 50(1)–(2)); deployer duty for emotion-recognition / biometric-categorisation notices and deepfake labelling (Art. 50(3)–(4)). Lives outside the Article 11 stack but cross-references it when end-user disclosure is needed.</t>
         </is>
       </c>
     </row>

--- a/09_ai-transparency-documentation/demo/model_card_demo.xlsx
+++ b/09_ai-transparency-documentation/demo/model_card_demo.xlsx
@@ -867,7 +867,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>[AML.T0051 LLM Prompt Injection] Prompt-injection via comments embedded in input source files; [AML.T0024.000 Infer Training Data Membership] data-exfiltration via crafted completions when the prompt contains secrets; [AML.T0048 External Harms] insecure-code suggestion when the prompt encodes a vulnerability pattern; [AML.T0040 ML Model Inference API Access] system-prompt fingerprinting by determined adversaries.</t>
+          <t>[AML.T0051 LLM Prompt Injection] Prompt-injection via comments embedded in input source files; [AML.T0024.000 Infer Training Data Membership] data-exfiltration via crafted completions when the prompt contains secrets; [AML.T0048 External Harms] insecure-code suggestion when the prompt encodes a vulnerability pattern; [AML.T0040 AI Model Inference API Access] system-prompt fingerprinting by determined adversaries.</t>
         </is>
       </c>
     </row>
